--- a/Result/profitability/4529.xlsx
+++ b/Result/profitability/4529.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.28</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.22875</v>
+        <v>-0.19375</v>
       </c>
       <c r="N2" t="n">
-        <v>55.40499999999999</v>
+        <v>51.6375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.05</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.17125</v>
+        <v>-0.15875</v>
       </c>
       <c r="N3" t="n">
-        <v>47.30125</v>
+        <v>44.2625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.265</v>
+        <v>-0.26</v>
       </c>
       <c r="N4" t="n">
-        <v>38.7825</v>
+        <v>35.8275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.29625</v>
+        <v>-0.285</v>
       </c>
       <c r="N5" t="n">
-        <v>31.755</v>
+        <v>29.075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.305</v>
+        <v>-0.29875</v>
       </c>
       <c r="N6" t="n">
-        <v>22.44375</v>
+        <v>19.6225</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.35375</v>
+        <v>-0.34875</v>
       </c>
       <c r="N7" t="n">
-        <v>11.58375</v>
+        <v>9.563750000000002</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3275</v>
+        <v>-0.3225</v>
       </c>
       <c r="N8" t="n">
-        <v>5.520000000000002</v>
+        <v>5.866250000000003</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9742,6 +9742,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4529</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-84.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="N75" t="n">
+        <v>59.81625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.04000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2352941176470589</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.770000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06906008476689118</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4090909090909091</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-21.43999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3333333333333333</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
